--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.55790809449956</v>
+        <v>6.428160065356178</v>
       </c>
       <c r="D2" t="n">
-        <v>41.36906023225237</v>
+        <v>6.722472287741009</v>
       </c>
       <c r="E2" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F2" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.92412815741691</v>
+        <v>4.537670825580249</v>
       </c>
       <c r="D3" t="n">
-        <v>29.72857872967628</v>
+        <v>4.830894043572395</v>
       </c>
       <c r="E3" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F3" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.93766849794723</v>
+        <v>2.427371130916426</v>
       </c>
       <c r="D4" t="n">
-        <v>13.16348925528913</v>
+        <v>2.139067003984484</v>
       </c>
       <c r="E4" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F4" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.66734162257242</v>
+        <v>10.83344301366802</v>
       </c>
       <c r="D5" t="n">
-        <v>64.99059625340344</v>
+        <v>10.56097189117806</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F5" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.07467732708241</v>
+        <v>5.374635065650892</v>
       </c>
       <c r="D6" t="n">
-        <v>31.19131020670739</v>
+        <v>5.06858790858995</v>
       </c>
       <c r="E6" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F6" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.08576756233665</v>
+        <v>6.838937228879706</v>
       </c>
       <c r="D7" t="n">
-        <v>40.22509026876895</v>
+        <v>6.536577168674955</v>
       </c>
       <c r="E7" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F7" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.80656280601925</v>
+        <v>3.381066455978128</v>
       </c>
       <c r="D8" t="n">
-        <v>19.38353326467631</v>
+        <v>3.1498241555099</v>
       </c>
       <c r="E8" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F8" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>57.10757123730041</v>
+        <v>9.279980326061317</v>
       </c>
       <c r="D9" t="n">
-        <v>56.71301487537455</v>
+        <v>9.215864917248364</v>
       </c>
       <c r="E9" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F9" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.75765769453173</v>
+        <v>5.160619375361406</v>
       </c>
       <c r="D10" t="n">
-        <v>31.28475576385141</v>
+        <v>5.083772811625855</v>
       </c>
       <c r="E10" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F10" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.3481321688163</v>
+        <v>5.581571477432649</v>
       </c>
       <c r="D11" t="n">
-        <v>30.36838260644645</v>
+        <v>4.934862173547548</v>
       </c>
       <c r="E11" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F11" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.55540528716233</v>
+        <v>5.940253359163878</v>
       </c>
       <c r="D12" t="n">
-        <v>2.864451069803553</v>
+        <v>0.4654732988430773</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F12" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.9404496235271</v>
+        <v>5.352823063823154</v>
       </c>
       <c r="D13" t="n">
-        <v>20.45185886856242</v>
+        <v>3.323427066141394</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F13" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>52.5809446534624</v>
+        <v>8.54440350618764</v>
       </c>
       <c r="D14" t="n">
-        <v>52.46824041220162</v>
+        <v>8.526089066982765</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F14" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>54.660611794684</v>
+        <v>8.882349416636151</v>
       </c>
       <c r="D15" t="n">
-        <v>54.63320142158437</v>
+        <v>8.877895231007461</v>
       </c>
       <c r="E15" t="n">
-        <v>13.9319575097748</v>
+        <v>2.263943095338405</v>
       </c>
       <c r="F15" t="n">
-        <v>17.26238812975524</v>
+        <v>2.805138071085226</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
